--- a/output/all-profiles.xlsx
+++ b/output/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7173" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7173" uniqueCount="742">
   <si>
     <t>Property</t>
   </si>
@@ -464,16 +464,23 @@
     <t>Definition of the measurement type</t>
   </si>
   <si>
-    <t xml:space="preserve">Definition of the measurement type of a HiMi device, e.g. that the device only measures tissue glucose. </t>
+    <t>Definition of the measurement type of a HiMi device, e.g. that the device only measures tissue glucose. Only codes from LOINC are allowed. Codes must be match to code in measurements, e.g from this ValueSet. : https://gematik.de/fhir/hdc/ValueSet/VS-Tissue-Glucose-CGM</t>
   </si>
   <si>
     <t>Note: For the OAuth scopes, so that the corresponding FHIR endpoint only returns the allowed device configuration that matches the measurements.</t>
   </si>
   <si>
-    <t>Only codes from LOINC are allowed. Codes must be match to code in measurements, e.g from this ValueSet. : https://gematik.de/fhir/hdc/ValueSet/VS-Tissue-Glucose-CGM</t>
-  </si>
-  <si>
-    <t>http://loinc.org/vs</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Describes the metric type.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/devicemetric-type</t>
   </si>
   <si>
     <t>DeviceMetric.unit</t>
@@ -688,7 +695,7 @@
     <t>Device_HiMi</t>
   </si>
   <si>
-    <t>2025-08-19T17:49:48+02:00</t>
+    <t>2025-08-20T09:32:40+02:00</t>
   </si>
   <si>
     <t>Device</t>
@@ -2627,7 +2634,7 @@
         <v>2</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23">
@@ -2635,7 +2642,7 @@
         <v>4</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24">
@@ -2651,7 +2658,7 @@
         <v>8</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26">
@@ -2679,7 +2686,7 @@
         <v>15</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30">
@@ -2735,7 +2742,7 @@
         <v>29</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38">
@@ -2743,7 +2750,7 @@
         <v>31</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39">
@@ -2775,7 +2782,7 @@
         <v>2</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="43">
@@ -2783,7 +2790,7 @@
         <v>4</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="44">
@@ -2799,7 +2806,7 @@
         <v>8</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="46">
@@ -2807,7 +2814,7 @@
         <v>10</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="47">
@@ -2853,7 +2860,7 @@
         <v>21</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="53">
@@ -2889,7 +2896,7 @@
         <v>29</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="58">
@@ -2897,7 +2904,7 @@
         <v>31</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="59">
@@ -2929,7 +2936,7 @@
         <v>2</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="63">
@@ -2937,7 +2944,7 @@
         <v>4</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="64">
@@ -2953,7 +2960,7 @@
         <v>8</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="66">
@@ -2961,7 +2968,7 @@
         <v>10</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="67">
@@ -3007,7 +3014,7 @@
         <v>21</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="73">
@@ -3043,7 +3050,7 @@
         <v>29</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="78">
@@ -3051,7 +3058,7 @@
         <v>31</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="79">
@@ -3099,13 +3106,13 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.09375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="43.70703125" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="7.93359375" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.08984375" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="139.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="81.0" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="51.0859375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.6953125" customWidth="true" bestFit="true"/>
@@ -4331,7 +4338,7 @@
         <v>20</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="U12" t="s" s="2">
         <v>20</v>
@@ -4349,10 +4356,10 @@
         <v>105</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AB12" t="s" s="2">
         <v>20</v>
@@ -4390,10 +4397,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
@@ -4419,13 +4426,13 @@
         <v>142</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P13" s="2"/>
       <c r="Q13" t="s" s="2">
@@ -4451,13 +4458,13 @@
         <v>20</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AB13" t="s" s="2">
         <v>20</v>
@@ -4475,7 +4482,7 @@
         <v>20</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>73</v>
@@ -4495,10 +4502,10 @@
         <v>3</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" t="s" s="2">
@@ -4521,13 +4528,13 @@
         <v>82</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -4578,7 +4585,7 @@
         <v>20</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>73</v>
@@ -4598,10 +4605,10 @@
         <v>3</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
@@ -4624,13 +4631,13 @@
         <v>82</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -4681,7 +4688,7 @@
         <v>20</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>73</v>
@@ -4701,10 +4708,10 @@
         <v>3</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
@@ -4730,10 +4737,10 @@
         <v>101</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -4760,13 +4767,13 @@
         <v>20</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AB16" t="s" s="2">
         <v>20</v>
@@ -4784,7 +4791,7 @@
         <v>20</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>73</v>
@@ -4804,10 +4811,10 @@
         <v>3</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
@@ -4833,10 +4840,10 @@
         <v>101</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -4863,13 +4870,13 @@
         <v>20</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AB17" t="s" s="2">
         <v>20</v>
@@ -4887,7 +4894,7 @@
         <v>20</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>73</v>
@@ -4907,10 +4914,10 @@
         <v>3</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
@@ -4936,10 +4943,10 @@
         <v>101</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -4966,13 +4973,13 @@
         <v>20</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AB18" t="s" s="2">
         <v>20</v>
@@ -4990,7 +4997,7 @@
         <v>20</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>81</v>
@@ -5010,10 +5017,10 @@
         <v>3</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
@@ -5036,13 +5043,13 @@
         <v>82</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -5093,7 +5100,7 @@
         <v>20</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>73</v>
@@ -5113,10 +5120,10 @@
         <v>3</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
@@ -5139,13 +5146,13 @@
         <v>82</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -5196,7 +5203,7 @@
         <v>20</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>73</v>
@@ -5216,10 +5223,10 @@
         <v>3</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -5242,13 +5249,13 @@
         <v>20</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -5299,7 +5306,7 @@
         <v>20</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>73</v>
@@ -5319,10 +5326,10 @@
         <v>3</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -5351,7 +5358,7 @@
         <v>126</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O22" t="s" s="2">
         <v>128</v>
@@ -5404,7 +5411,7 @@
         <v>20</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>73</v>
@@ -5424,14 +5431,14 @@
         <v>3</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" t="s" s="2">
@@ -5453,10 +5460,10 @@
         <v>125</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O23" t="s" s="2">
         <v>128</v>
@@ -5511,7 +5518,7 @@
         <v>20</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>73</v>
@@ -5531,10 +5538,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
@@ -5560,10 +5567,10 @@
         <v>101</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -5590,13 +5597,13 @@
         <v>20</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AB24" t="s" s="2">
         <v>20</v>
@@ -5614,7 +5621,7 @@
         <v>20</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>73</v>
@@ -5634,10 +5641,10 @@
         <v>3</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
@@ -5663,10 +5670,10 @@
         <v>101</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -5693,13 +5700,13 @@
         <v>20</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AB25" t="s" s="2">
         <v>20</v>
@@ -5717,7 +5724,7 @@
         <v>20</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>73</v>
@@ -5737,10 +5744,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -5763,13 +5770,13 @@
         <v>82</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -5820,7 +5827,7 @@
         <v>20</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>73</v>
@@ -5837,13 +5844,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
@@ -5869,10 +5876,10 @@
         <v>75</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -5923,7 +5930,7 @@
         <v>20</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>73</v>
@@ -5940,13 +5947,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -6045,13 +6052,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -6148,13 +6155,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -6253,13 +6260,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -6358,13 +6365,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -6463,13 +6470,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -6568,13 +6575,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -6673,13 +6680,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -6780,13 +6787,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -6815,10 +6822,10 @@
         <v>138</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P36" s="2"/>
       <c r="Q36" t="s" s="2">
@@ -6868,7 +6875,7 @@
         <v>20</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>73</v>
@@ -6885,13 +6892,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -6914,13 +6921,13 @@
         <v>20</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -6971,7 +6978,7 @@
         <v>20</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>73</v>
@@ -6988,13 +6995,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -7017,16 +7024,16 @@
         <v>82</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P38" s="2"/>
       <c r="Q38" t="s" s="2">
@@ -7076,7 +7083,7 @@
         <v>20</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>73</v>
@@ -7093,13 +7100,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -7122,13 +7129,13 @@
         <v>20</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
@@ -7179,7 +7186,7 @@
         <v>20</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>73</v>
@@ -7196,13 +7203,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -7231,7 +7238,7 @@
         <v>126</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>128</v>
@@ -7284,7 +7291,7 @@
         <v>20</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>73</v>
@@ -7301,17 +7308,17 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" t="s" s="2">
@@ -7333,10 +7340,10 @@
         <v>125</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>128</v>
@@ -7391,7 +7398,7 @@
         <v>20</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>73</v>
@@ -7408,17 +7415,17 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" t="s" s="2">
@@ -7437,13 +7444,13 @@
         <v>82</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
@@ -7494,7 +7501,7 @@
         <v>20</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>73</v>
@@ -7511,17 +7518,17 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" t="s" s="2">
@@ -7543,10 +7550,10 @@
         <v>95</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" s="2"/>
@@ -7597,7 +7604,7 @@
         <v>20</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>73</v>
@@ -7614,13 +7621,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -7646,14 +7653,14 @@
         <v>95</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q44" t="s" s="2">
         <v>20</v>
@@ -7702,7 +7709,7 @@
         <v>20</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>73</v>
@@ -7719,17 +7726,17 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" t="s" s="2">
@@ -7748,16 +7755,16 @@
         <v>82</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P45" s="2"/>
       <c r="Q45" t="s" s="2">
@@ -7807,7 +7814,7 @@
         <v>20</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>73</v>
@@ -7824,17 +7831,17 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" t="s" s="2">
@@ -7853,16 +7860,16 @@
         <v>82</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P46" s="2"/>
       <c r="Q46" t="s" s="2">
@@ -7912,7 +7919,7 @@
         <v>20</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>73</v>
@@ -7929,13 +7936,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7961,14 +7968,14 @@
         <v>101</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q47" t="s" s="2">
         <v>20</v>
@@ -7993,13 +8000,13 @@
         <v>20</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AB47" t="s" s="2">
         <v>20</v>
@@ -8017,7 +8024,7 @@
         <v>20</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>73</v>
@@ -8034,13 +8041,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -8066,13 +8073,13 @@
         <v>101</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P48" s="2"/>
       <c r="Q48" t="s" s="2">
@@ -8098,13 +8105,13 @@
         <v>20</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AB48" t="s" s="2">
         <v>20</v>
@@ -8122,7 +8129,7 @@
         <v>20</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>73</v>
@@ -8139,13 +8146,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -8171,10 +8178,10 @@
         <v>142</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
@@ -8201,13 +8208,13 @@
         <v>20</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AB49" t="s" s="2">
         <v>20</v>
@@ -8225,7 +8232,7 @@
         <v>20</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>73</v>
@@ -8242,17 +8249,17 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" t="s" s="2">
@@ -8271,16 +8278,16 @@
         <v>20</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P50" s="2"/>
       <c r="Q50" t="s" s="2">
@@ -8330,7 +8337,7 @@
         <v>20</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>73</v>
@@ -8347,13 +8354,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -8376,13 +8383,13 @@
         <v>20</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
@@ -8433,7 +8440,7 @@
         <v>20</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>73</v>
@@ -8450,13 +8457,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -8479,13 +8486,13 @@
         <v>20</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
@@ -8536,7 +8543,7 @@
         <v>20</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>73</v>
@@ -8553,13 +8560,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -8582,13 +8589,13 @@
         <v>20</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" s="2"/>
@@ -8639,7 +8646,7 @@
         <v>20</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>73</v>
@@ -8656,13 +8663,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8685,13 +8692,13 @@
         <v>20</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" s="2"/>
@@ -8742,7 +8749,7 @@
         <v>20</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>73</v>
@@ -8759,13 +8766,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8788,16 +8795,16 @@
         <v>20</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P55" s="2"/>
       <c r="Q55" t="s" s="2">
@@ -8847,7 +8854,7 @@
         <v>20</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>73</v>
@@ -8864,13 +8871,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8893,13 +8900,13 @@
         <v>20</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" s="2"/>
@@ -8950,7 +8957,7 @@
         <v>20</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>73</v>
@@ -8967,13 +8974,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8996,13 +9003,13 @@
         <v>20</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
@@ -9053,7 +9060,7 @@
         <v>20</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>73</v>
@@ -9070,13 +9077,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -9105,7 +9112,7 @@
         <v>126</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>128</v>
@@ -9158,7 +9165,7 @@
         <v>20</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>73</v>
@@ -9175,17 +9182,17 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" t="s" s="2">
@@ -9207,10 +9214,10 @@
         <v>125</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>128</v>
@@ -9265,7 +9272,7 @@
         <v>20</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>73</v>
@@ -9282,17 +9289,17 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" t="s" s="2">
@@ -9311,13 +9318,13 @@
         <v>20</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
@@ -9368,7 +9375,7 @@
         <v>20</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>81</v>
@@ -9385,13 +9392,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -9417,10 +9424,10 @@
         <v>101</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" s="2"/>
@@ -9447,13 +9454,13 @@
         <v>20</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AA61" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AB61" t="s" s="2">
         <v>20</v>
@@ -9471,7 +9478,7 @@
         <v>20</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>81</v>
@@ -9488,13 +9495,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -9517,13 +9524,13 @@
         <v>20</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
@@ -9574,7 +9581,7 @@
         <v>20</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>73</v>
@@ -9591,13 +9598,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -9620,16 +9627,16 @@
         <v>20</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
@@ -9679,7 +9686,7 @@
         <v>20</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>73</v>
@@ -9696,13 +9703,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -9728,10 +9735,10 @@
         <v>142</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
@@ -9758,13 +9765,13 @@
         <v>20</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AA64" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AB64" t="s" s="2">
         <v>20</v>
@@ -9782,7 +9789,7 @@
         <v>20</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>73</v>
@@ -9799,13 +9806,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9828,13 +9835,13 @@
         <v>20</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" s="2"/>
@@ -9885,7 +9892,7 @@
         <v>20</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>73</v>
@@ -9902,13 +9909,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -9931,13 +9938,13 @@
         <v>20</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" s="2"/>
@@ -9988,7 +9995,7 @@
         <v>20</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>73</v>
@@ -10005,13 +10012,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -10040,7 +10047,7 @@
         <v>126</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>128</v>
@@ -10093,7 +10100,7 @@
         <v>20</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>73</v>
@@ -10110,17 +10117,17 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" t="s" s="2">
@@ -10142,10 +10149,10 @@
         <v>125</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>128</v>
@@ -10200,7 +10207,7 @@
         <v>20</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>73</v>
@@ -10217,17 +10224,17 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" t="s" s="2">
@@ -10249,10 +10256,10 @@
         <v>142</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" s="2"/>
@@ -10303,7 +10310,7 @@
         <v>20</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>81</v>
@@ -10320,13 +10327,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -10349,13 +10356,13 @@
         <v>20</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" s="2"/>
@@ -10406,7 +10413,7 @@
         <v>20</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>73</v>
@@ -10423,13 +10430,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -10452,13 +10459,13 @@
         <v>20</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" s="2"/>
@@ -10509,7 +10516,7 @@
         <v>20</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>73</v>
@@ -10526,13 +10533,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -10555,13 +10562,13 @@
         <v>20</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" s="2"/>
@@ -10612,7 +10619,7 @@
         <v>20</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>73</v>
@@ -10629,13 +10636,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -10664,7 +10671,7 @@
         <v>126</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>128</v>
@@ -10717,7 +10724,7 @@
         <v>20</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>73</v>
@@ -10734,17 +10741,17 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" t="s" s="2">
@@ -10766,10 +10773,10 @@
         <v>125</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>128</v>
@@ -10824,7 +10831,7 @@
         <v>20</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>73</v>
@@ -10841,17 +10848,17 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" t="s" s="2">
@@ -10873,10 +10880,10 @@
         <v>142</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" s="2"/>
@@ -10927,7 +10934,7 @@
         <v>20</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>73</v>
@@ -10944,13 +10951,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10976,10 +10983,10 @@
         <v>137</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" s="2"/>
@@ -11030,7 +11037,7 @@
         <v>20</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>73</v>
@@ -11047,13 +11054,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -11076,13 +11083,13 @@
         <v>20</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" s="2"/>
@@ -11133,7 +11140,7 @@
         <v>20</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>81</v>
@@ -11150,13 +11157,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -11179,13 +11186,13 @@
         <v>20</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" s="2"/>
@@ -11236,7 +11243,7 @@
         <v>20</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>73</v>
@@ -11253,13 +11260,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -11282,13 +11289,13 @@
         <v>20</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
@@ -11339,7 +11346,7 @@
         <v>20</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>73</v>
@@ -11356,13 +11363,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -11391,7 +11398,7 @@
         <v>126</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O80" t="s" s="2">
         <v>128</v>
@@ -11444,7 +11451,7 @@
         <v>20</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>73</v>
@@ -11461,17 +11468,17 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" t="s" s="2">
@@ -11493,10 +11500,10 @@
         <v>125</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O81" t="s" s="2">
         <v>128</v>
@@ -11551,7 +11558,7 @@
         <v>20</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>73</v>
@@ -11568,13 +11575,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -11600,10 +11607,10 @@
         <v>142</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" s="2"/>
@@ -11654,7 +11661,7 @@
         <v>20</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>81</v>
@@ -11671,13 +11678,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -11700,13 +11707,13 @@
         <v>20</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" s="2"/>
@@ -11757,7 +11764,7 @@
         <v>20</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>73</v>
@@ -11774,13 +11781,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -11806,10 +11813,10 @@
         <v>142</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
@@ -11860,7 +11867,7 @@
         <v>20</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>73</v>
@@ -11877,13 +11884,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -11906,17 +11913,17 @@
         <v>20</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q85" t="s" s="2">
         <v>20</v>
@@ -11965,7 +11972,7 @@
         <v>20</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>73</v>
@@ -11982,13 +11989,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -12011,13 +12018,13 @@
         <v>20</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
@@ -12068,7 +12075,7 @@
         <v>20</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>73</v>
@@ -12085,13 +12092,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -12114,16 +12121,16 @@
         <v>20</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P87" s="2"/>
       <c r="Q87" t="s" s="2">
@@ -12173,7 +12180,7 @@
         <v>20</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>73</v>
@@ -12190,13 +12197,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -12219,17 +12226,17 @@
         <v>20</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q88" t="s" s="2">
         <v>20</v>
@@ -12278,7 +12285,7 @@
         <v>20</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>73</v>
@@ -12295,13 +12302,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -12327,13 +12334,13 @@
         <v>95</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P89" s="2"/>
       <c r="Q89" t="s" s="2">
@@ -12383,7 +12390,7 @@
         <v>20</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>73</v>
@@ -12400,13 +12407,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -12429,13 +12436,13 @@
         <v>20</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
@@ -12486,7 +12493,7 @@
         <v>20</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>73</v>
@@ -12503,13 +12510,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -12535,10 +12542,10 @@
         <v>142</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
@@ -12589,7 +12596,7 @@
         <v>20</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>73</v>
@@ -12606,13 +12613,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -12635,13 +12642,13 @@
         <v>20</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
@@ -12692,7 +12699,7 @@
         <v>20</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>73</v>
@@ -12709,17 +12716,17 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" t="s" s="2">
@@ -12741,13 +12748,13 @@
         <v>75</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P93" s="2"/>
       <c r="Q93" t="s" s="2">
@@ -12797,7 +12804,7 @@
         <v>20</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>73</v>
@@ -12809,18 +12816,18 @@
         <v>20</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -12919,13 +12926,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -13022,13 +13029,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -13127,13 +13134,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -13232,13 +13239,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -13337,13 +13344,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -13442,13 +13449,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -13547,13 +13554,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -13654,13 +13661,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13686,14 +13693,14 @@
         <v>137</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q102" t="s" s="2">
         <v>20</v>
@@ -13742,7 +13749,7 @@
         <v>20</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>73</v>
@@ -13759,17 +13766,17 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" t="s" s="2">
@@ -13788,17 +13795,17 @@
         <v>82</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q103" t="s" s="2">
         <v>20</v>
@@ -13847,7 +13854,7 @@
         <v>20</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>73</v>
@@ -13864,17 +13871,17 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" t="s" s="2">
@@ -13893,16 +13900,16 @@
         <v>82</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P104" s="2"/>
       <c r="Q104" t="s" s="2">
@@ -13952,7 +13959,7 @@
         <v>20</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>73</v>
@@ -13969,13 +13976,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -14001,16 +14008,16 @@
         <v>101</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P105" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q105" t="s" s="2">
         <v>20</v>
@@ -14035,13 +14042,13 @@
         <v>20</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AA105" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AB105" t="s" s="2">
         <v>20</v>
@@ -14059,7 +14066,7 @@
         <v>20</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>81</v>
@@ -14076,13 +14083,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -14108,16 +14115,16 @@
         <v>142</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P106" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q106" t="s" s="2">
         <v>20</v>
@@ -14145,10 +14152,10 @@
         <v>105</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA106" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AB106" t="s" s="2">
         <v>20</v>
@@ -14166,7 +14173,7 @@
         <v>20</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>73</v>
@@ -14183,17 +14190,17 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" t="s" s="2">
@@ -14215,16 +14222,16 @@
         <v>142</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P107" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Q107" t="s" s="2">
         <v>20</v>
@@ -14249,13 +14256,13 @@
         <v>20</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA107" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AB107" t="s" s="2">
         <v>20</v>
@@ -14273,7 +14280,7 @@
         <v>20</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>81</v>
@@ -14290,13 +14297,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -14319,19 +14326,19 @@
         <v>82</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P108" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Q108" t="s" s="2">
         <v>20</v>
@@ -14380,7 +14387,7 @@
         <v>20</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>73</v>
@@ -14397,13 +14404,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -14426,16 +14433,16 @@
         <v>82</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P109" s="2"/>
       <c r="Q109" t="s" s="2">
@@ -14485,7 +14492,7 @@
         <v>20</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>73</v>
@@ -14502,17 +14509,17 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" t="s" s="2">
@@ -14531,19 +14538,19 @@
         <v>82</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P110" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Q110" t="s" s="2">
         <v>20</v>
@@ -14592,7 +14599,7 @@
         <v>20</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>73</v>
@@ -14609,17 +14616,17 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" t="s" s="2">
@@ -14638,19 +14645,19 @@
         <v>82</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P111" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Q111" t="s" s="2">
         <v>20</v>
@@ -14699,7 +14706,7 @@
         <v>20</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>73</v>
@@ -14716,13 +14723,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -14745,16 +14752,16 @@
         <v>82</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P112" s="2"/>
       <c r="Q112" t="s" s="2">
@@ -14804,7 +14811,7 @@
         <v>20</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>73</v>
@@ -14821,13 +14828,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -14850,17 +14857,17 @@
         <v>82</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="Q113" t="s" s="2">
         <v>20</v>
@@ -14909,7 +14916,7 @@
         <v>20</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>73</v>
@@ -14926,13 +14933,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -14955,19 +14962,19 @@
         <v>82</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P114" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="Q114" t="s" s="2">
         <v>20</v>
@@ -15016,7 +15023,7 @@
         <v>20</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>73</v>
@@ -15025,7 +15032,7 @@
         <v>81</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>93</v>
@@ -15033,13 +15040,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -15065,16 +15072,16 @@
         <v>142</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P115" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="Q115" t="s" s="2">
         <v>20</v>
@@ -15099,13 +15106,13 @@
         <v>20</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AA115" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AB115" t="s" s="2">
         <v>20</v>
@@ -15123,7 +15130,7 @@
         <v>20</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>73</v>
@@ -15132,7 +15139,7 @@
         <v>81</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>93</v>
@@ -15140,17 +15147,17 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" t="s" s="2">
@@ -15172,16 +15179,16 @@
         <v>142</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P116" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Q116" t="s" s="2">
         <v>20</v>
@@ -15206,13 +15213,13 @@
         <v>20</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA116" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AB116" t="s" s="2">
         <v>20</v>
@@ -15230,7 +15237,7 @@
         <v>20</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>73</v>
@@ -15247,13 +15254,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -15276,19 +15283,19 @@
         <v>20</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P117" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Q117" t="s" s="2">
         <v>20</v>
@@ -15337,7 +15344,7 @@
         <v>20</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AH117" t="s" s="2">
         <v>73</v>
@@ -15354,13 +15361,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -15386,13 +15393,13 @@
         <v>142</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P118" s="2"/>
       <c r="Q118" t="s" s="2">
@@ -15418,13 +15425,13 @@
         <v>20</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AA118" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AB118" t="s" s="2">
         <v>20</v>
@@ -15442,7 +15449,7 @@
         <v>20</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>73</v>
@@ -15459,13 +15466,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -15491,16 +15498,16 @@
         <v>142</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P119" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="Q119" t="s" s="2">
         <v>20</v>
@@ -15525,13 +15532,13 @@
         <v>20</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AA119" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AB119" t="s" s="2">
         <v>20</v>
@@ -15549,7 +15556,7 @@
         <v>20</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>73</v>
@@ -15566,13 +15573,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -15595,16 +15602,16 @@
         <v>20</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P120" s="2"/>
       <c r="Q120" t="s" s="2">
@@ -15654,7 +15661,7 @@
         <v>20</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>73</v>
@@ -15671,13 +15678,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -15700,16 +15707,16 @@
         <v>20</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P121" s="2"/>
       <c r="Q121" t="s" s="2">
@@ -15759,7 +15766,7 @@
         <v>20</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>73</v>
@@ -15776,13 +15783,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -15805,19 +15812,19 @@
         <v>20</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P122" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="Q122" t="s" s="2">
         <v>20</v>
@@ -15866,7 +15873,7 @@
         <v>20</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>73</v>
@@ -15878,18 +15885,18 @@
         <v>20</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -15912,13 +15919,13 @@
         <v>20</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" s="2"/>
@@ -15969,7 +15976,7 @@
         <v>20</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>73</v>
@@ -15986,13 +15993,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -16021,7 +16028,7 @@
         <v>126</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O124" t="s" s="2">
         <v>128</v>
@@ -16074,7 +16081,7 @@
         <v>20</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>73</v>
@@ -16091,17 +16098,17 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F125" s="2"/>
       <c r="G125" t="s" s="2">
@@ -16123,10 +16130,10 @@
         <v>125</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O125" t="s" s="2">
         <v>128</v>
@@ -16181,7 +16188,7 @@
         <v>20</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>73</v>
@@ -16198,13 +16205,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -16227,13 +16234,13 @@
         <v>20</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" s="2"/>
@@ -16284,7 +16291,7 @@
         <v>20</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>73</v>
@@ -16293,7 +16300,7 @@
         <v>81</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>93</v>
@@ -16301,13 +16308,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -16330,13 +16337,13 @@
         <v>20</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" s="2"/>
@@ -16387,16 +16394,16 @@
         <v>20</v>
       </c>
       <c r="AG127" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>93</v>
@@ -16404,13 +16411,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -16436,16 +16443,16 @@
         <v>142</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P128" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="Q128" t="s" s="2">
         <v>20</v>
@@ -16473,10 +16480,10 @@
         <v>105</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AA128" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AB128" t="s" s="2">
         <v>20</v>
@@ -16494,7 +16501,7 @@
         <v>20</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>73</v>
@@ -16511,13 +16518,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -16543,16 +16550,16 @@
         <v>142</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="P129" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="Q129" t="s" s="2">
         <v>20</v>
@@ -16577,13 +16584,13 @@
         <v>20</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AA129" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AB129" t="s" s="2">
         <v>20</v>
@@ -16601,7 +16608,7 @@
         <v>20</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>73</v>
@@ -16618,13 +16625,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -16647,17 +16654,17 @@
         <v>20</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="Q130" t="s" s="2">
         <v>20</v>
@@ -16706,7 +16713,7 @@
         <v>20</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>73</v>
@@ -16723,13 +16730,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -16752,13 +16759,13 @@
         <v>20</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" s="2"/>
@@ -16809,7 +16816,7 @@
         <v>20</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>73</v>
@@ -16826,13 +16833,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -16855,16 +16862,16 @@
         <v>82</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P132" s="2"/>
       <c r="Q132" t="s" s="2">
@@ -16914,7 +16921,7 @@
         <v>20</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>73</v>
@@ -16931,13 +16938,13 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -16960,16 +16967,16 @@
         <v>82</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P133" s="2"/>
       <c r="Q133" t="s" s="2">
@@ -17019,7 +17026,7 @@
         <v>20</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>73</v>
@@ -17036,13 +17043,13 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
@@ -17065,19 +17072,19 @@
         <v>82</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="P134" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="Q134" t="s" s="2">
         <v>20</v>
@@ -17126,7 +17133,7 @@
         <v>20</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>73</v>
@@ -17143,13 +17150,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
@@ -17172,13 +17179,13 @@
         <v>20</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" s="2"/>
@@ -17229,7 +17236,7 @@
         <v>20</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>73</v>
@@ -17246,13 +17253,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -17281,7 +17288,7 @@
         <v>126</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O136" t="s" s="2">
         <v>128</v>
@@ -17334,7 +17341,7 @@
         <v>20</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AH136" t="s" s="2">
         <v>73</v>
@@ -17351,17 +17358,17 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F137" s="2"/>
       <c r="G137" t="s" s="2">
@@ -17383,10 +17390,10 @@
         <v>125</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O137" t="s" s="2">
         <v>128</v>
@@ -17441,7 +17448,7 @@
         <v>20</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>73</v>
@@ -17458,13 +17465,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -17490,16 +17497,16 @@
         <v>142</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="P138" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Q138" t="s" s="2">
         <v>20</v>
@@ -17524,13 +17531,13 @@
         <v>20</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AA138" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AB138" t="s" s="2">
         <v>20</v>
@@ -17548,7 +17555,7 @@
         <v>20</v>
       </c>
       <c r="AG138" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AH138" t="s" s="2">
         <v>81</v>
@@ -17565,13 +17572,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -17594,19 +17601,19 @@
         <v>82</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="P139" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="Q139" t="s" s="2">
         <v>20</v>
@@ -17655,7 +17662,7 @@
         <v>20</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>73</v>
@@ -17672,13 +17679,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -17704,16 +17711,16 @@
         <v>142</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P140" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="Q140" t="s" s="2">
         <v>20</v>
@@ -17738,13 +17745,13 @@
         <v>20</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AA140" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AB140" t="s" s="2">
         <v>20</v>
@@ -17762,7 +17769,7 @@
         <v>20</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>73</v>
@@ -17771,7 +17778,7 @@
         <v>81</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>93</v>
@@ -17779,17 +17786,17 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F141" s="2"/>
       <c r="G141" t="s" s="2">
@@ -17811,16 +17818,16 @@
         <v>142</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P141" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Q141" t="s" s="2">
         <v>20</v>
@@ -17845,13 +17852,13 @@
         <v>20</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA141" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AB141" t="s" s="2">
         <v>20</v>
@@ -17869,7 +17876,7 @@
         <v>20</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>73</v>
@@ -17886,13 +17893,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -17918,16 +17925,16 @@
         <v>75</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P142" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="Q142" t="s" s="2">
         <v>20</v>
@@ -17976,7 +17983,7 @@
         <v>20</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>73</v>
@@ -17993,17 +18000,17 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F143" s="2"/>
       <c r="G143" t="s" s="2">
@@ -18025,13 +18032,13 @@
         <v>75</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P143" s="2"/>
       <c r="Q143" t="s" s="2">
@@ -18081,7 +18088,7 @@
         <v>20</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>73</v>
@@ -18093,18 +18100,18 @@
         <v>20</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -18203,13 +18210,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -18306,13 +18313,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -18411,13 +18418,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -18516,13 +18523,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -18621,13 +18628,13 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -18726,13 +18733,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -18831,13 +18838,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -18938,13 +18945,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -18970,14 +18977,14 @@
         <v>137</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q152" t="s" s="2">
         <v>20</v>
@@ -19026,7 +19033,7 @@
         <v>20</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>73</v>
@@ -19043,17 +19050,17 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F153" s="2"/>
       <c r="G153" t="s" s="2">
@@ -19072,17 +19079,17 @@
         <v>82</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q153" t="s" s="2">
         <v>20</v>
@@ -19131,7 +19138,7 @@
         <v>20</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AH153" t="s" s="2">
         <v>73</v>
@@ -19148,17 +19155,17 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F154" s="2"/>
       <c r="G154" t="s" s="2">
@@ -19177,16 +19184,16 @@
         <v>82</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P154" s="2"/>
       <c r="Q154" t="s" s="2">
@@ -19236,7 +19243,7 @@
         <v>20</v>
       </c>
       <c r="AG154" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AH154" t="s" s="2">
         <v>73</v>
@@ -19253,13 +19260,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -19285,16 +19292,16 @@
         <v>101</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P155" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q155" t="s" s="2">
         <v>20</v>
@@ -19319,13 +19326,13 @@
         <v>20</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AA155" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AB155" t="s" s="2">
         <v>20</v>
@@ -19343,7 +19350,7 @@
         <v>20</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>81</v>
@@ -19360,13 +19367,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -19392,16 +19399,16 @@
         <v>142</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P156" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q156" t="s" s="2">
         <v>20</v>
@@ -19429,10 +19436,10 @@
         <v>105</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA156" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AB156" t="s" s="2">
         <v>20</v>
@@ -19450,7 +19457,7 @@
         <v>20</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AH156" t="s" s="2">
         <v>73</v>
@@ -19467,17 +19474,17 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F157" s="2"/>
       <c r="G157" t="s" s="2">
@@ -19499,16 +19506,16 @@
         <v>142</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P157" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Q157" t="s" s="2">
         <v>20</v>
@@ -19533,13 +19540,13 @@
         <v>20</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AA157" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AB157" t="s" s="2">
         <v>20</v>
@@ -19557,7 +19564,7 @@
         <v>20</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AH157" t="s" s="2">
         <v>81</v>
@@ -19574,13 +19581,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -19603,19 +19610,19 @@
         <v>82</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P158" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Q158" t="s" s="2">
         <v>20</v>
@@ -19664,7 +19671,7 @@
         <v>20</v>
       </c>
       <c r="AG158" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AH158" t="s" s="2">
         <v>73</v>
@@ -19681,13 +19688,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -19710,16 +19717,16 @@
         <v>82</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P159" s="2"/>
       <c r="Q159" t="s" s="2">
@@ -19769,7 +19776,7 @@
         <v>20</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH159" t="s" s="2">
         <v>73</v>
@@ -19786,17 +19793,17 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F160" s="2"/>
       <c r="G160" t="s" s="2">
@@ -19815,19 +19822,19 @@
         <v>82</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P160" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Q160" t="s" s="2">
         <v>20</v>
@@ -19876,7 +19883,7 @@
         <v>20</v>
       </c>
       <c r="AG160" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AH160" t="s" s="2">
         <v>73</v>
@@ -19893,17 +19900,17 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F161" s="2"/>
       <c r="G161" t="s" s="2">
@@ -19922,19 +19929,19 @@
         <v>82</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P161" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Q161" t="s" s="2">
         <v>20</v>
@@ -19983,7 +19990,7 @@
         <v>20</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>73</v>
@@ -20000,13 +20007,13 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -20029,13 +20036,13 @@
         <v>20</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" s="2"/>
@@ -20086,7 +20093,7 @@
         <v>20</v>
       </c>
       <c r="AG162" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH162" t="s" s="2">
         <v>73</v>
@@ -20103,13 +20110,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -20138,7 +20145,7 @@
         <v>126</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O163" t="s" s="2">
         <v>128</v>
@@ -20179,19 +20186,19 @@
         <v>20</v>
       </c>
       <c r="AC163" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AD163" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AE163" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AH163" t="s" s="2">
         <v>73</v>
@@ -20208,13 +20215,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -20237,16 +20244,16 @@
         <v>82</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P164" s="2"/>
       <c r="Q164" t="s" s="2">
@@ -20296,7 +20303,7 @@
         <v>20</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>73</v>
@@ -20305,7 +20312,7 @@
         <v>81</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>93</v>
@@ -20313,13 +20320,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -20342,23 +20349,23 @@
         <v>82</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="P165" s="2"/>
       <c r="Q165" t="s" s="2">
         <v>20</v>
       </c>
       <c r="R165" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>20</v>
@@ -20403,7 +20410,7 @@
         <v>20</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>73</v>
@@ -20412,7 +20419,7 @@
         <v>81</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AK165" t="s" s="2">
         <v>93</v>
@@ -20420,13 +20427,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -20449,16 +20456,16 @@
         <v>82</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P166" s="2"/>
       <c r="Q166" t="s" s="2">
@@ -20508,7 +20515,7 @@
         <v>20</v>
       </c>
       <c r="AG166" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AH166" t="s" s="2">
         <v>73</v>
@@ -20525,13 +20532,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -20554,17 +20561,17 @@
         <v>82</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="Q167" t="s" s="2">
         <v>20</v>
@@ -20613,7 +20620,7 @@
         <v>20</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>73</v>
@@ -20630,13 +20637,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -20659,19 +20666,19 @@
         <v>82</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P168" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="Q168" t="s" s="2">
         <v>20</v>
@@ -20720,7 +20727,7 @@
         <v>20</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>73</v>
@@ -20729,7 +20736,7 @@
         <v>81</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>93</v>
@@ -20737,13 +20744,13 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -20766,13 +20773,13 @@
         <v>20</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" s="2"/>
@@ -20823,7 +20830,7 @@
         <v>20</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>73</v>
@@ -20840,13 +20847,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -20875,7 +20882,7 @@
         <v>126</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O170" t="s" s="2">
         <v>128</v>
@@ -20916,19 +20923,19 @@
         <v>20</v>
       </c>
       <c r="AC170" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AD170" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AE170" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>73</v>
@@ -20945,13 +20952,13 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
@@ -20974,13 +20981,13 @@
         <v>82</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" s="2"/>
@@ -21031,7 +21038,7 @@
         <v>20</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AH171" t="s" s="2">
         <v>81</v>
@@ -21048,13 +21055,13 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -21077,13 +21084,13 @@
         <v>20</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" s="2"/>
@@ -21134,7 +21141,7 @@
         <v>20</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH172" t="s" s="2">
         <v>73</v>
@@ -21151,13 +21158,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -21186,7 +21193,7 @@
         <v>126</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>128</v>
@@ -21227,19 +21234,19 @@
         <v>20</v>
       </c>
       <c r="AC173" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AD173" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AE173" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG173" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AH173" t="s" s="2">
         <v>73</v>
@@ -21256,13 +21263,13 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -21285,19 +21292,19 @@
         <v>82</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P174" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Q174" t="s" s="2">
         <v>20</v>
@@ -21346,7 +21353,7 @@
         <v>20</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>73</v>
@@ -21363,13 +21370,13 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -21395,20 +21402,20 @@
         <v>101</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="Q175" t="s" s="2">
         <v>20</v>
       </c>
       <c r="R175" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>20</v>
@@ -21429,13 +21436,13 @@
         <v>20</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AA175" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AB175" t="s" s="2">
         <v>20</v>
@@ -21453,7 +21460,7 @@
         <v>20</v>
       </c>
       <c r="AG175" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AH175" t="s" s="2">
         <v>73</v>
@@ -21470,13 +21477,13 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" t="s" s="2">
@@ -21499,17 +21506,17 @@
         <v>82</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="Q176" t="s" s="2">
         <v>20</v>
@@ -21558,7 +21565,7 @@
         <v>20</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AH176" t="s" s="2">
         <v>73</v>
@@ -21575,13 +21582,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
@@ -21607,14 +21614,14 @@
         <v>95</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="Q177" t="s" s="2">
         <v>20</v>
@@ -21663,7 +21670,7 @@
         <v>20</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AH177" t="s" s="2">
         <v>73</v>
@@ -21672,7 +21679,7 @@
         <v>81</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>93</v>
@@ -21680,13 +21687,13 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" t="s" s="2">
@@ -21712,16 +21719,16 @@
         <v>101</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="P178" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="Q178" t="s" s="2">
         <v>20</v>
@@ -21746,13 +21753,13 @@
         <v>20</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AA178" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AB178" t="s" s="2">
         <v>20</v>
@@ -21770,7 +21777,7 @@
         <v>20</v>
       </c>
       <c r="AG178" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AH178" t="s" s="2">
         <v>73</v>
@@ -21787,13 +21794,13 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D179" s="2"/>
       <c r="E179" t="s" s="2">
@@ -21816,16 +21823,16 @@
         <v>82</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="P179" s="2"/>
       <c r="Q179" t="s" s="2">
@@ -21875,7 +21882,7 @@
         <v>20</v>
       </c>
       <c r="AG179" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AH179" t="s" s="2">
         <v>81</v>
@@ -21892,13 +21899,13 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
@@ -21921,13 +21928,13 @@
         <v>82</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" s="2"/>
@@ -21935,7 +21942,7 @@
         <v>20</v>
       </c>
       <c r="R180" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="S180" t="s" s="2">
         <v>20</v>
@@ -21980,7 +21987,7 @@
         <v>20</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>73</v>
@@ -21997,13 +22004,13 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" t="s" s="2">
@@ -22026,13 +22033,13 @@
         <v>82</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" s="2"/>
@@ -22083,7 +22090,7 @@
         <v>20</v>
       </c>
       <c r="AG181" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AH181" t="s" s="2">
         <v>73</v>
@@ -22100,13 +22107,13 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D182" s="2"/>
       <c r="E182" t="s" s="2">
@@ -22129,13 +22136,13 @@
         <v>82</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" s="2"/>
@@ -22186,7 +22193,7 @@
         <v>20</v>
       </c>
       <c r="AG182" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AH182" t="s" s="2">
         <v>73</v>
@@ -22203,13 +22210,13 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" t="s" s="2">
@@ -22232,16 +22239,16 @@
         <v>82</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="P183" s="2"/>
       <c r="Q183" t="s" s="2">
@@ -22291,7 +22298,7 @@
         <v>20</v>
       </c>
       <c r="AG183" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AH183" t="s" s="2">
         <v>81</v>
@@ -22308,13 +22315,13 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" t="s" s="2">
@@ -22337,16 +22344,16 @@
         <v>20</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="P184" s="2"/>
       <c r="Q184" t="s" s="2">
@@ -22396,7 +22403,7 @@
         <v>20</v>
       </c>
       <c r="AG184" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AH184" t="s" s="2">
         <v>73</v>
@@ -22413,13 +22420,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" t="s" s="2">
@@ -22445,16 +22452,16 @@
         <v>142</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P185" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="Q185" t="s" s="2">
         <v>20</v>
@@ -22479,13 +22486,13 @@
         <v>20</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AA185" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AB185" t="s" s="2">
         <v>20</v>
@@ -22503,7 +22510,7 @@
         <v>20</v>
       </c>
       <c r="AG185" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AH185" t="s" s="2">
         <v>73</v>
@@ -22512,7 +22519,7 @@
         <v>81</v>
       </c>
       <c r="AJ185" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AK185" t="s" s="2">
         <v>93</v>
@@ -22520,17 +22527,17 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F186" s="2"/>
       <c r="G186" t="s" s="2">
@@ -22552,16 +22559,16 @@
         <v>142</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P186" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Q186" t="s" s="2">
         <v>20</v>
@@ -22586,13 +22593,13 @@
         <v>20</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA186" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AB186" t="s" s="2">
         <v>20</v>
@@ -22610,7 +22617,7 @@
         <v>20</v>
       </c>
       <c r="AG186" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AH186" t="s" s="2">
         <v>73</v>
@@ -22627,13 +22634,13 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" t="s" s="2">
@@ -22656,19 +22663,19 @@
         <v>20</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P187" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Q187" t="s" s="2">
         <v>20</v>
@@ -22717,7 +22724,7 @@
         <v>20</v>
       </c>
       <c r="AG187" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AH187" t="s" s="2">
         <v>73</v>
@@ -22734,13 +22741,13 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" t="s" s="2">
@@ -22766,13 +22773,13 @@
         <v>142</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P188" s="2"/>
       <c r="Q188" t="s" s="2">
@@ -22798,13 +22805,13 @@
         <v>20</v>
       </c>
       <c r="Y188" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z188" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AA188" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AB188" t="s" s="2">
         <v>20</v>
@@ -22822,7 +22829,7 @@
         <v>20</v>
       </c>
       <c r="AG188" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AH188" t="s" s="2">
         <v>73</v>
@@ -22839,13 +22846,13 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" t="s" s="2">
@@ -22871,16 +22878,16 @@
         <v>142</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P189" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="Q189" t="s" s="2">
         <v>20</v>
@@ -22905,13 +22912,13 @@
         <v>20</v>
       </c>
       <c r="Y189" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z189" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AA189" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AB189" t="s" s="2">
         <v>20</v>
@@ -22929,7 +22936,7 @@
         <v>20</v>
       </c>
       <c r="AG189" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AH189" t="s" s="2">
         <v>73</v>
@@ -22946,13 +22953,13 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" t="s" s="2">
@@ -22975,16 +22982,16 @@
         <v>20</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P190" s="2"/>
       <c r="Q190" t="s" s="2">
@@ -23034,7 +23041,7 @@
         <v>20</v>
       </c>
       <c r="AG190" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AH190" t="s" s="2">
         <v>73</v>
@@ -23051,13 +23058,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" t="s" s="2">
@@ -23080,16 +23087,16 @@
         <v>20</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P191" s="2"/>
       <c r="Q191" t="s" s="2">
@@ -23139,7 +23146,7 @@
         <v>20</v>
       </c>
       <c r="AG191" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AH191" t="s" s="2">
         <v>73</v>
@@ -23156,13 +23163,13 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" t="s" s="2">
@@ -23185,19 +23192,19 @@
         <v>20</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P192" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="Q192" t="s" s="2">
         <v>20</v>
@@ -23246,7 +23253,7 @@
         <v>20</v>
       </c>
       <c r="AG192" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AH192" t="s" s="2">
         <v>73</v>
@@ -23258,18 +23265,18 @@
         <v>20</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
@@ -23292,13 +23299,13 @@
         <v>20</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" s="2"/>
@@ -23349,7 +23356,7 @@
         <v>20</v>
       </c>
       <c r="AG193" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH193" t="s" s="2">
         <v>73</v>
@@ -23366,13 +23373,13 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" t="s" s="2">
@@ -23401,7 +23408,7 @@
         <v>126</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O194" t="s" s="2">
         <v>128</v>
@@ -23454,7 +23461,7 @@
         <v>20</v>
       </c>
       <c r="AG194" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AH194" t="s" s="2">
         <v>73</v>
@@ -23471,17 +23478,17 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F195" s="2"/>
       <c r="G195" t="s" s="2">
@@ -23503,10 +23510,10 @@
         <v>125</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O195" t="s" s="2">
         <v>128</v>
@@ -23561,7 +23568,7 @@
         <v>20</v>
       </c>
       <c r="AG195" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AH195" t="s" s="2">
         <v>73</v>
@@ -23578,13 +23585,13 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" t="s" s="2">
@@ -23607,13 +23614,13 @@
         <v>20</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" s="2"/>
@@ -23664,7 +23671,7 @@
         <v>20</v>
       </c>
       <c r="AG196" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AH196" t="s" s="2">
         <v>73</v>
@@ -23673,7 +23680,7 @@
         <v>81</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AK196" t="s" s="2">
         <v>93</v>
@@ -23681,13 +23688,13 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" t="s" s="2">
@@ -23710,13 +23717,13 @@
         <v>20</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" s="2"/>
@@ -23767,16 +23774,16 @@
         <v>20</v>
       </c>
       <c r="AG197" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AH197" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI197" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ197" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="AH197" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ197" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="AK197" t="s" s="2">
         <v>93</v>
@@ -23784,13 +23791,13 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" t="s" s="2">
@@ -23816,16 +23823,16 @@
         <v>142</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O198" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P198" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="Q198" t="s" s="2">
         <v>20</v>
@@ -23853,10 +23860,10 @@
         <v>105</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AA198" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AB198" t="s" s="2">
         <v>20</v>
@@ -23874,7 +23881,7 @@
         <v>20</v>
       </c>
       <c r="AG198" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AH198" t="s" s="2">
         <v>73</v>
@@ -23891,13 +23898,13 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" t="s" s="2">
@@ -23923,16 +23930,16 @@
         <v>142</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="P199" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="Q199" t="s" s="2">
         <v>20</v>
@@ -23957,13 +23964,13 @@
         <v>20</v>
       </c>
       <c r="Y199" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z199" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AA199" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AB199" t="s" s="2">
         <v>20</v>
@@ -23981,7 +23988,7 @@
         <v>20</v>
       </c>
       <c r="AG199" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AH199" t="s" s="2">
         <v>73</v>
@@ -23998,13 +24005,13 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" t="s" s="2">
@@ -24027,17 +24034,17 @@
         <v>20</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="Q200" t="s" s="2">
         <v>20</v>
@@ -24086,7 +24093,7 @@
         <v>20</v>
       </c>
       <c r="AG200" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AH200" t="s" s="2">
         <v>73</v>
@@ -24103,13 +24110,13 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" t="s" s="2">
@@ -24132,13 +24139,13 @@
         <v>20</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" s="2"/>
@@ -24189,7 +24196,7 @@
         <v>20</v>
       </c>
       <c r="AG201" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AH201" t="s" s="2">
         <v>73</v>
@@ -24206,13 +24213,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" t="s" s="2">
@@ -24235,16 +24242,16 @@
         <v>82</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O202" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P202" s="2"/>
       <c r="Q202" t="s" s="2">
@@ -24294,7 +24301,7 @@
         <v>20</v>
       </c>
       <c r="AG202" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AH202" t="s" s="2">
         <v>73</v>
@@ -24311,13 +24318,13 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" t="s" s="2">
@@ -24340,16 +24347,16 @@
         <v>82</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P203" s="2"/>
       <c r="Q203" t="s" s="2">
@@ -24399,7 +24406,7 @@
         <v>20</v>
       </c>
       <c r="AG203" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AH203" t="s" s="2">
         <v>73</v>
@@ -24416,13 +24423,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" t="s" s="2">
@@ -24445,19 +24452,19 @@
         <v>82</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="P204" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="Q204" t="s" s="2">
         <v>20</v>
@@ -24506,7 +24513,7 @@
         <v>20</v>
       </c>
       <c r="AG204" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AH204" t="s" s="2">
         <v>73</v>
@@ -24523,13 +24530,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" t="s" s="2">
@@ -24552,13 +24559,13 @@
         <v>20</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" s="2"/>
@@ -24609,7 +24616,7 @@
         <v>20</v>
       </c>
       <c r="AG205" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH205" t="s" s="2">
         <v>73</v>
@@ -24626,13 +24633,13 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" t="s" s="2">
@@ -24661,7 +24668,7 @@
         <v>126</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O206" t="s" s="2">
         <v>128</v>
@@ -24714,7 +24721,7 @@
         <v>20</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>73</v>
@@ -24731,17 +24738,17 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F207" s="2"/>
       <c r="G207" t="s" s="2">
@@ -24763,10 +24770,10 @@
         <v>125</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O207" t="s" s="2">
         <v>128</v>
@@ -24821,7 +24828,7 @@
         <v>20</v>
       </c>
       <c r="AG207" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AH207" t="s" s="2">
         <v>73</v>
@@ -24838,13 +24845,13 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" t="s" s="2">
@@ -24870,16 +24877,16 @@
         <v>142</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O208" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="P208" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Q208" t="s" s="2">
         <v>20</v>
@@ -24904,13 +24911,13 @@
         <v>20</v>
       </c>
       <c r="Y208" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z208" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AA208" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AB208" t="s" s="2">
         <v>20</v>
@@ -24928,7 +24935,7 @@
         <v>20</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AH208" t="s" s="2">
         <v>81</v>
@@ -24945,13 +24952,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" t="s" s="2">
@@ -24974,19 +24981,19 @@
         <v>82</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O209" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="P209" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="Q209" t="s" s="2">
         <v>20</v>
@@ -25035,7 +25042,7 @@
         <v>20</v>
       </c>
       <c r="AG209" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AH209" t="s" s="2">
         <v>73</v>
@@ -25052,13 +25059,13 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" t="s" s="2">
@@ -25084,16 +25091,16 @@
         <v>142</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P210" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="Q210" t="s" s="2">
         <v>20</v>
@@ -25118,13 +25125,13 @@
         <v>20</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AA210" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AB210" t="s" s="2">
         <v>20</v>
@@ -25142,7 +25149,7 @@
         <v>20</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AH210" t="s" s="2">
         <v>73</v>
@@ -25151,7 +25158,7 @@
         <v>81</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AK210" t="s" s="2">
         <v>93</v>
@@ -25159,17 +25166,17 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F211" s="2"/>
       <c r="G211" t="s" s="2">
@@ -25191,16 +25198,16 @@
         <v>142</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P211" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Q211" t="s" s="2">
         <v>20</v>
@@ -25225,13 +25232,13 @@
         <v>20</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z211" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA211" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AB211" t="s" s="2">
         <v>20</v>
@@ -25249,7 +25256,7 @@
         <v>20</v>
       </c>
       <c r="AG211" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AH211" t="s" s="2">
         <v>73</v>
@@ -25266,13 +25273,13 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" t="s" s="2">
@@ -25298,16 +25305,16 @@
         <v>75</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O212" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P212" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="Q212" t="s" s="2">
         <v>20</v>
@@ -25356,7 +25363,7 @@
         <v>20</v>
       </c>
       <c r="AG212" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AH212" t="s" s="2">
         <v>73</v>

--- a/output/all-profiles.xlsx
+++ b/output/all-profiles.xlsx
@@ -695,7 +695,7 @@
     <t>Device_HiMi</t>
   </si>
   <si>
-    <t>2025-08-20T09:32:40+02:00</t>
+    <t>2025-08-21T10:18:14+02:00</t>
   </si>
   <si>
     <t>Device</t>
@@ -8580,7 +8580,7 @@
         <v>81</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>20</v>
@@ -9509,13 +9509,13 @@
       </c>
       <c r="F62" s="2"/>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>20</v>

--- a/output/all-profiles.xlsx
+++ b/output/all-profiles.xlsx
@@ -695,7 +695,7 @@
     <t>Device_HiMi</t>
   </si>
   <si>
-    <t>2025-08-21T10:18:14+02:00</t>
+    <t>2025-08-21T11:34:25+02:00</t>
   </si>
   <si>
     <t>Device</t>

--- a/output/all-profiles.xlsx
+++ b/output/all-profiles.xlsx
@@ -695,7 +695,7 @@
     <t>Device_HiMi</t>
   </si>
   <si>
-    <t>2025-08-21T11:34:25+02:00</t>
+    <t>2025-08-21T15:49:15+02:00</t>
   </si>
   <si>
     <t>Device</t>
